--- a/artfynd/A 23963-2022 artfynd.xlsx
+++ b/artfynd/A 23963-2022 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118299375</v>
+        <v>118298743</v>
       </c>
       <c r="B2" t="n">
         <v>57659</v>
@@ -711,7 +711,7 @@
       <c r="I2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -720,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>443187</v>
+        <v>443310</v>
       </c>
       <c r="R2" t="n">
-        <v>6264311</v>
+        <v>6264331</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -750,12 +750,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-05-28</t>
+          <t>2024-04-24</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-05-28</t>
+          <t>2024-04-24</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -786,7 +786,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118298743</v>
+        <v>118298742</v>
       </c>
       <c r="B3" t="n">
         <v>57659</v>
@@ -820,21 +820,16 @@
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Loshult, Sk</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>443310</v>
+        <v>443297</v>
       </c>
       <c r="R3" t="n">
-        <v>6264331</v>
+        <v>6264353</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -897,7 +892,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118298742</v>
+        <v>118299375</v>
       </c>
       <c r="B4" t="n">
         <v>57659</v>
@@ -931,16 +926,21 @@
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Loshult, Sk</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>443297</v>
+        <v>443187</v>
       </c>
       <c r="R4" t="n">
-        <v>6264353</v>
+        <v>6264311</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -967,12 +967,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-04-24</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-04-24</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 23963-2022 artfynd.xlsx
+++ b/artfynd/A 23963-2022 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118298743</v>
+        <v>118298742</v>
       </c>
       <c r="B2" t="n">
         <v>57659</v>
@@ -709,21 +709,16 @@
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Loshult, Sk</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>443310</v>
+        <v>443297</v>
       </c>
       <c r="R2" t="n">
-        <v>6264331</v>
+        <v>6264353</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -786,7 +781,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118298742</v>
+        <v>118298743</v>
       </c>
       <c r="B3" t="n">
         <v>57659</v>
@@ -820,16 +815,21 @@
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Loshult, Sk</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>443297</v>
+        <v>443310</v>
       </c>
       <c r="R3" t="n">
-        <v>6264353</v>
+        <v>6264331</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>

--- a/artfynd/A 23963-2022 artfynd.xlsx
+++ b/artfynd/A 23963-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118298742</v>
+        <v>118298741</v>
       </c>
       <c r="B2" t="n">
-        <v>57659</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>443297</v>
+        <v>443187</v>
       </c>
       <c r="R2" t="n">
-        <v>6264353</v>
+        <v>6264240</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -781,15 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118298743</v>
+        <v>118298742</v>
       </c>
       <c r="B3" t="n">
-        <v>57659</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -815,21 +805,16 @@
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Loshult, Sk</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>443310</v>
+        <v>443297</v>
       </c>
       <c r="R3" t="n">
-        <v>6264331</v>
+        <v>6264353</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -892,15 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118299375</v>
+        <v>118298743</v>
       </c>
       <c r="B4" t="n">
-        <v>57659</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -928,7 +908,7 @@
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -937,10 +917,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>443187</v>
+        <v>443310</v>
       </c>
       <c r="R4" t="n">
-        <v>6264311</v>
+        <v>6264331</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -967,12 +947,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-05-28</t>
+          <t>2024-04-24</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-05-28</t>
+          <t>2024-04-24</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,6 +976,112 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>118299375</v>
+      </c>
+      <c r="B5" t="n">
+        <v>58327</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Loshult, Sk</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>443187</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6264311</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Osby</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Loshult</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-05-28</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-05-28</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Eric Bjuringer</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Eric Bjuringer</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
         <is>
           <t>Ecogain</t>
         </is>
